--- a/Lab_4/data/partB/param_optimization_process/v100_k40_s100_results.xlsx
+++ b/Lab_4/data/partB/param_optimization_process/v100_k40_s100_results.xlsx
@@ -518,43 +518,43 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G2" t="n">
+        <v>9</v>
+      </c>
+      <c r="H2" t="n">
         <v>3</v>
-      </c>
-      <c r="F2" t="n">
-        <v>7</v>
-      </c>
-      <c r="G2" t="n">
-        <v>6</v>
-      </c>
-      <c r="H2" t="n">
-        <v>4</v>
       </c>
       <c r="I2" t="n">
         <v>24</v>
       </c>
       <c r="J2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" t="n">
+        <v>8</v>
+      </c>
+      <c r="L2" t="n">
         <v>3</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>9</v>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="n">
         <v>4</v>
-      </c>
-      <c r="M2" t="n">
-        <v>6</v>
-      </c>
-      <c r="N2" t="n">
-        <v>5</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -573,34 +573,34 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
         <v>3</v>
       </c>
-      <c r="E3" t="n">
-        <v>5</v>
-      </c>
       <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
         <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -609,7 +609,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
@@ -628,7 +628,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -646,13 +646,13 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M4" t="n">
         <v>2</v>
@@ -661,7 +661,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -677,19 +677,19 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G5" t="n">
         <v>8</v>
-      </c>
-      <c r="G5" t="n">
-        <v>6</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -698,13 +698,13 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>4</v>
       </c>
       <c r="O5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P5" t="n">
         <v>5</v>
@@ -726,49 +726,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C6" t="n">
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>7</v>
       </c>
       <c r="J6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -787,34 +787,34 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G7" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
         <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -830,46 +830,46 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G8" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H8" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L8" t="n">
         <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="N8" t="n">
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>3</v>
@@ -882,49 +882,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L9" t="n">
         <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -937,10 +937,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -958,22 +958,22 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -986,7 +986,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -998,22 +998,22 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G11" t="n">
         <v>22</v>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
+        <v>22</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>29</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>22</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1022,13 +1022,13 @@
         <v>4</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
+        <v>2</v>
+      </c>
+      <c r="P11" t="n">
         <v>3</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1038,7 +1038,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
         <v>19</v>
@@ -1047,7 +1047,7 @@
         <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
@@ -1062,16 +1062,16 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>3</v>
@@ -1080,7 +1080,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1090,49 +1090,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G13" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4</v>
+      </c>
+      <c r="J13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K13" t="n">
         <v>1</v>
-      </c>
-      <c r="I13" t="n">
-        <v>5</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="N13" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1145,37 +1145,37 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N14" t="n">
         <v>50</v>
@@ -1184,7 +1184,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -1218,13 +1218,13 @@
         <v>5</v>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
         <v>2</v>
@@ -1249,7 +1249,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D16" t="n">
         <v>2</v>
@@ -1258,34 +1258,34 @@
         <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
       <c r="L16" t="n">
+        <v>4</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3</v>
+      </c>
+      <c r="N16" t="n">
         <v>2</v>
       </c>
-      <c r="M16" t="n">
-        <v>2</v>
-      </c>
-      <c r="N16" t="n">
-        <v>4</v>
-      </c>
       <c r="O16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
         <v>62</v>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1692,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3919,7 +3919,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4089,7 +4089,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -6469,7 +6469,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -6588,7 +6588,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -6656,7 +6656,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6843,7 +6843,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -6962,7 +6962,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -7047,7 +7047,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7081,7 +7081,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7132,7 +7132,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -7149,7 +7149,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7251,7 +7251,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -7319,7 +7319,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -7438,7 +7438,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7540,7 +7540,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7557,7 +7557,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7693,7 +7693,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7778,7 +7778,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -7829,7 +7829,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -7846,7 +7846,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7897,7 +7897,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7948,7 +7948,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -8050,7 +8050,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -8084,7 +8084,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8135,7 +8135,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -8288,7 +8288,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -8492,7 +8492,7 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -8611,7 +8611,7 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -8747,7 +8747,7 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8832,7 +8832,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8917,7 +8917,7 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9325,7 +9325,7 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9376,7 +9376,7 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9410,7 +9410,7 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9478,7 +9478,7 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9495,7 +9495,7 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -9546,7 +9546,7 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9631,7 +9631,7 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -9648,7 +9648,7 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9750,7 +9750,7 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -9835,7 +9835,7 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9988,7 +9988,7 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -10073,7 +10073,7 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -10158,7 +10158,7 @@
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -10243,7 +10243,7 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -10345,7 +10345,7 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10413,7 +10413,7 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10600,7 +10600,7 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10634,7 +10634,7 @@
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10702,7 +10702,7 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -10770,7 +10770,7 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -11059,7 +11059,7 @@
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -11110,7 +11110,7 @@
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11144,7 +11144,7 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -11246,7 +11246,7 @@
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11314,7 +11314,7 @@
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11331,7 +11331,7 @@
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11382,7 +11382,7 @@
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11399,7 +11399,7 @@
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11416,7 +11416,7 @@
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -11501,7 +11501,7 @@
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -11535,7 +11535,7 @@
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11552,7 +11552,7 @@
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11586,7 +11586,7 @@
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11603,7 @@
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -11620,7 +11620,7 @@
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -11688,7 +11688,7 @@
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11773,7 +11773,7 @@
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11790,7 +11790,7 @@
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -11807,7 +11807,7 @@
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11824,7 +11824,7 @@
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11994,7 +11994,7 @@
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12028,7 +12028,7 @@
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12113,7 +12113,7 @@
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -12181,7 +12181,7 @@
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12317,7 +12317,7 @@
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12351,7 +12351,7 @@
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12436,7 +12436,7 @@
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12453,7 +12453,7 @@
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12504,7 +12504,7 @@
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -12521,7 +12521,7 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -12555,7 +12555,7 @@
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12606,7 +12606,7 @@
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12640,7 +12640,7 @@
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12657,7 +12657,7 @@
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12674,7 +12674,7 @@
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12691,7 +12691,7 @@
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12725,7 +12725,7 @@
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -12810,7 +12810,7 @@
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12861,7 +12861,7 @@
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12878,7 +12878,7 @@
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12912,7 +12912,7 @@
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13048,7 +13048,7 @@
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -13065,7 +13065,7 @@
       </c>
       <c r="C692" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13082,7 +13082,7 @@
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13099,7 +13099,7 @@
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13116,7 +13116,7 @@
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13133,7 +13133,7 @@
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -13150,7 +13150,7 @@
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -13184,7 +13184,7 @@
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13201,7 +13201,7 @@
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13235,7 +13235,7 @@
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13269,7 +13269,7 @@
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -13303,7 +13303,7 @@
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -13337,7 +13337,7 @@
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -13354,7 +13354,7 @@
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -13405,7 +13405,7 @@
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13456,7 +13456,7 @@
       </c>
       <c r="C715" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13575,7 +13575,7 @@
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -13592,7 +13592,7 @@
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13660,7 +13660,7 @@
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13711,7 +13711,7 @@
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13728,7 +13728,7 @@
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -13762,7 +13762,7 @@
       </c>
       <c r="C733" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13779,7 +13779,7 @@
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="C743" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14000,7 +14000,7 @@
       </c>
       <c r="C747" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14068,7 +14068,7 @@
       </c>
       <c r="C751" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14153,7 +14153,7 @@
       </c>
       <c r="C756" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14170,7 +14170,7 @@
       </c>
       <c r="C757" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14255,7 +14255,7 @@
       </c>
       <c r="C762" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14323,7 +14323,7 @@
       </c>
       <c r="C766" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14340,7 +14340,7 @@
       </c>
       <c r="C767" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -14357,7 +14357,7 @@
       </c>
       <c r="C768" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -14374,7 +14374,7 @@
       </c>
       <c r="C769" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -14391,7 +14391,7 @@
       </c>
       <c r="C770" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14425,7 +14425,7 @@
       </c>
       <c r="C772" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -14459,7 +14459,7 @@
       </c>
       <c r="C774" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -14527,7 +14527,7 @@
       </c>
       <c r="C778" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14544,7 +14544,7 @@
       </c>
       <c r="C779" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14629,7 +14629,7 @@
       </c>
       <c r="C784" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -14765,7 +14765,7 @@
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -14782,7 +14782,7 @@
       </c>
       <c r="C793" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -14816,7 +14816,7 @@
       </c>
       <c r="C795" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14833,7 +14833,7 @@
       </c>
       <c r="C796" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14901,7 +14901,7 @@
       </c>
       <c r="C800" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C803" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15190,7 +15190,7 @@
       </c>
       <c r="C817" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -15343,7 +15343,7 @@
       </c>
       <c r="C826" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -15411,7 +15411,7 @@
       </c>
       <c r="C830" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15632,7 +15632,7 @@
       </c>
       <c r="C843" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15819,7 +15819,7 @@
       </c>
       <c r="C854" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15853,7 +15853,7 @@
       </c>
       <c r="C856" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15989,7 +15989,7 @@
       </c>
       <c r="C864" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16023,7 +16023,7 @@
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16074,7 +16074,7 @@
       </c>
       <c r="C869" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -16210,7 +16210,7 @@
       </c>
       <c r="C877" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16261,7 +16261,7 @@
       </c>
       <c r="C880" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16431,7 +16431,7 @@
       </c>
       <c r="C890" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16465,7 +16465,7 @@
       </c>
       <c r="C892" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16533,7 +16533,7 @@
       </c>
       <c r="C896" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16601,7 +16601,7 @@
       </c>
       <c r="C900" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16652,7 +16652,7 @@
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -16737,7 +16737,7 @@
       </c>
       <c r="C908" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -16771,7 +16771,7 @@
       </c>
       <c r="C910" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -16856,7 +16856,7 @@
       </c>
       <c r="C915" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -16873,7 +16873,7 @@
       </c>
       <c r="C916" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -16890,7 +16890,7 @@
       </c>
       <c r="C917" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -16941,7 +16941,7 @@
       </c>
       <c r="C920" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17094,7 +17094,7 @@
       </c>
       <c r="C929" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -17111,7 +17111,7 @@
       </c>
       <c r="C930" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17145,7 +17145,7 @@
       </c>
       <c r="C932" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -17230,7 +17230,7 @@
       </c>
       <c r="C937" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -17315,7 +17315,7 @@
       </c>
       <c r="C942" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17434,7 +17434,7 @@
       </c>
       <c r="C949" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17485,7 +17485,7 @@
       </c>
       <c r="C952" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17536,7 +17536,7 @@
       </c>
       <c r="C955" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17638,7 +17638,7 @@
       </c>
       <c r="C961" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -17706,7 +17706,7 @@
       </c>
       <c r="C965" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17893,7 +17893,7 @@
       </c>
       <c r="C976" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -17961,7 +17961,7 @@
       </c>
       <c r="C980" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -18046,7 +18046,7 @@
       </c>
       <c r="C985" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18063,7 +18063,7 @@
       </c>
       <c r="C986" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -18080,7 +18080,7 @@
       </c>
       <c r="C987" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -18114,7 +18114,7 @@
       </c>
       <c r="C989" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18267,7 +18267,7 @@
       </c>
       <c r="C998" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18471,7 +18471,7 @@
       </c>
       <c r="C1010" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18556,7 +18556,7 @@
       </c>
       <c r="C1015" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18590,7 +18590,7 @@
       </c>
       <c r="C1017" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -18607,7 +18607,7 @@
       </c>
       <c r="C1018" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18641,7 +18641,7 @@
       </c>
       <c r="C1020" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18692,7 +18692,7 @@
       </c>
       <c r="C1023" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18726,7 +18726,7 @@
       </c>
       <c r="C1025" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18743,7 +18743,7 @@
       </c>
       <c r="C1026" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18777,7 +18777,7 @@
       </c>
       <c r="C1028" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18879,7 +18879,7 @@
       </c>
       <c r="C1034" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18947,7 +18947,7 @@
       </c>
       <c r="C1038" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -18964,7 +18964,7 @@
       </c>
       <c r="C1039" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19083,7 +19083,7 @@
       </c>
       <c r="C1046" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19117,7 +19117,7 @@
       </c>
       <c r="C1048" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19185,7 +19185,7 @@
       </c>
       <c r="C1052" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19236,7 +19236,7 @@
       </c>
       <c r="C1055" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C1061" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -19355,7 +19355,7 @@
       </c>
       <c r="C1062" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19525,7 +19525,7 @@
       </c>
       <c r="C1072" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="C1076" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -19729,7 +19729,7 @@
       </c>
       <c r="C1084" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19865,7 +19865,7 @@
       </c>
       <c r="C1092" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19967,7 +19967,7 @@
       </c>
       <c r="C1098" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19984,7 +19984,7 @@
       </c>
       <c r="C1099" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -20001,7 +20001,7 @@
       </c>
       <c r="C1100" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -20086,7 +20086,7 @@
       </c>
       <c r="C1105" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="C1109" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -20222,7 +20222,7 @@
       </c>
       <c r="C1113" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C1115" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -20290,7 +20290,7 @@
       </c>
       <c r="C1117" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -20409,7 +20409,7 @@
       </c>
       <c r="C1124" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -20528,7 +20528,7 @@
       </c>
       <c r="C1131" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -20596,7 +20596,7 @@
       </c>
       <c r="C1135" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -20647,7 +20647,7 @@
       </c>
       <c r="C1138" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -20681,7 +20681,7 @@
       </c>
       <c r="C1140" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -20732,7 +20732,7 @@
       </c>
       <c r="C1143" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20851,7 +20851,7 @@
       </c>
       <c r="C1150" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -20885,7 +20885,7 @@
       </c>
       <c r="C1152" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -20902,7 +20902,7 @@
       </c>
       <c r="C1153" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21072,7 +21072,7 @@
       </c>
       <c r="C1163" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21140,7 +21140,7 @@
       </c>
       <c r="C1167" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21225,7 +21225,7 @@
       </c>
       <c r="C1172" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -21259,7 +21259,7 @@
       </c>
       <c r="C1174" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21276,7 +21276,7 @@
       </c>
       <c r="C1175" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21310,7 +21310,7 @@
       </c>
       <c r="C1177" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -21344,7 +21344,7 @@
       </c>
       <c r="C1179" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21378,7 +21378,7 @@
       </c>
       <c r="C1181" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21412,7 +21412,7 @@
       </c>
       <c r="C1183" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21514,7 +21514,7 @@
       </c>
       <c r="C1189" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -21565,7 +21565,7 @@
       </c>
       <c r="C1192" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21599,7 +21599,7 @@
       </c>
       <c r="C1194" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21650,7 +21650,7 @@
       </c>
       <c r="C1197" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -21752,7 +21752,7 @@
       </c>
       <c r="C1203" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21820,7 +21820,7 @@
       </c>
       <c r="C1207" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21854,7 +21854,7 @@
       </c>
       <c r="C1209" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -21871,7 +21871,7 @@
       </c>
       <c r="C1210" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21888,7 +21888,7 @@
       </c>
       <c r="C1211" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21922,7 +21922,7 @@
       </c>
       <c r="C1213" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22041,7 +22041,7 @@
       </c>
       <c r="C1220" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22058,7 +22058,7 @@
       </c>
       <c r="C1221" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22075,7 +22075,7 @@
       </c>
       <c r="C1222" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -22143,7 +22143,7 @@
       </c>
       <c r="C1226" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22160,7 +22160,7 @@
       </c>
       <c r="C1227" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22279,7 +22279,7 @@
       </c>
       <c r="C1234" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22415,7 +22415,7 @@
       </c>
       <c r="C1242" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22449,7 +22449,7 @@
       </c>
       <c r="C1244" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -22500,7 +22500,7 @@
       </c>
       <c r="C1247" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22517,7 +22517,7 @@
       </c>
       <c r="C1248" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22534,7 +22534,7 @@
       </c>
       <c r="C1249" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22721,7 +22721,7 @@
       </c>
       <c r="C1260" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22755,7 +22755,7 @@
       </c>
       <c r="C1262" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -22772,7 +22772,7 @@
       </c>
       <c r="C1263" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -22789,7 +22789,7 @@
       </c>
       <c r="C1264" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22823,7 +22823,7 @@
       </c>
       <c r="C1266" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22840,7 +22840,7 @@
       </c>
       <c r="C1267" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22857,7 +22857,7 @@
       </c>
       <c r="C1268" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -22908,7 +22908,7 @@
       </c>
       <c r="C1271" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22925,7 +22925,7 @@
       </c>
       <c r="C1272" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -22993,7 +22993,7 @@
       </c>
       <c r="C1276" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23180,7 +23180,7 @@
       </c>
       <c r="C1287" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -23197,7 +23197,7 @@
       </c>
       <c r="C1288" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -23299,7 +23299,7 @@
       </c>
       <c r="C1294" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -23333,7 +23333,7 @@
       </c>
       <c r="C1296" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23639,7 +23639,7 @@
       </c>
       <c r="C1314" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -23656,7 +23656,7 @@
       </c>
       <c r="C1315" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -23724,7 +23724,7 @@
       </c>
       <c r="C1319" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -23775,7 +23775,7 @@
       </c>
       <c r="C1322" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24047,7 +24047,7 @@
       </c>
       <c r="C1338" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -24183,7 +24183,7 @@
       </c>
       <c r="C1346" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -24217,7 +24217,7 @@
       </c>
       <c r="C1348" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -24353,7 +24353,7 @@
       </c>
       <c r="C1356" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -24506,7 +24506,7 @@
       </c>
       <c r="C1365" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -24778,7 +24778,7 @@
       </c>
       <c r="C1381" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24795,7 +24795,7 @@
       </c>
       <c r="C1382" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -25050,7 +25050,7 @@
       </c>
       <c r="C1397" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -25084,7 +25084,7 @@
       </c>
       <c r="C1399" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -25118,7 +25118,7 @@
       </c>
       <c r="C1401" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -25152,7 +25152,7 @@
       </c>
       <c r="C1403" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -25169,7 +25169,7 @@
       </c>
       <c r="C1404" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -25186,7 +25186,7 @@
       </c>
       <c r="C1405" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25237,7 +25237,7 @@
       </c>
       <c r="C1408" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25322,7 +25322,7 @@
       </c>
       <c r="C1413" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25441,7 +25441,7 @@
       </c>
       <c r="C1420" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25492,7 +25492,7 @@
       </c>
       <c r="C1423" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -25526,7 +25526,7 @@
       </c>
       <c r="C1425" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -25662,7 +25662,7 @@
       </c>
       <c r="C1433" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25781,7 +25781,7 @@
       </c>
       <c r="C1440" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -25798,7 +25798,7 @@
       </c>
       <c r="C1441" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -25866,7 +25866,7 @@
       </c>
       <c r="C1445" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -25951,7 +25951,7 @@
       </c>
       <c r="C1450" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26087,7 +26087,7 @@
       </c>
       <c r="C1458" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -26223,7 +26223,7 @@
       </c>
       <c r="C1466" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26240,7 +26240,7 @@
       </c>
       <c r="C1467" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26291,7 +26291,7 @@
       </c>
       <c r="C1470" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -26342,7 +26342,7 @@
       </c>
       <c r="C1473" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26495,7 +26495,7 @@
       </c>
       <c r="C1482" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -26563,7 +26563,7 @@
       </c>
       <c r="C1486" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26614,7 +26614,7 @@
       </c>
       <c r="C1489" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -26631,7 +26631,7 @@
       </c>
       <c r="C1490" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26750,7 +26750,7 @@
       </c>
       <c r="C1497" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
